--- a/leads/sabusinessdirectories_contacts (2).xlsx
+++ b/leads/sabusinessdirectories_contacts (2).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manu\Documents\Web dev\Projects\unlimited_webscraper\leads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="122">
   <si>
     <t>Name</t>
   </si>
@@ -291,9 +291,6 @@
     <t>SUPER MAC TUNE UP &amp; WHEEL ALIGNMENT</t>
   </si>
   <si>
-    <t>047-532 2246 FAX: 047-532 2597</t>
-  </si>
-  <si>
     <t>EAST LONDON SHIPYARD (PTY) LTD</t>
   </si>
   <si>
@@ -321,9 +318,6 @@
     <t>LABOUR LAW MANAGEMENT CONSULTING</t>
   </si>
   <si>
-    <t>No. : 011 888 7944 Fax No. : 011 782 0664 Cellular No. : 082 8522 973 E-Mail Add. ivan@labourlawadvice.co.za Website Add. : www.labourlawadvice.co.za TRADE HEADINGS 1) LABOUR LAW CONSULTANTS</t>
-  </si>
-  <si>
     <t>GARDEN COURT</t>
   </si>
   <si>
@@ -363,31 +357,34 @@
     <t>W &amp; A JOINERY TRUST</t>
   </si>
   <si>
-    <t>NUMBER : (011) 334 0869</t>
-  </si>
-  <si>
     <t>PROFILE PERSONNEL</t>
   </si>
   <si>
-    <t>043-726 0308 EMAIL: jakie@profilepersonnel.co.za TRADE HEADING RECRUITMENT CONSULTANTS</t>
-  </si>
-  <si>
     <t>SIVIWE JAYIYA CONSTRUCTION.</t>
   </si>
   <si>
-    <t>043-470 0419 FAX: 043-740 0432 CELL: 083 421 6544</t>
-  </si>
-  <si>
     <t>TV DOCTOR</t>
   </si>
   <si>
-    <t>041-582 1788 EMAIL: tvdoctpe@telkomsa.net</t>
-  </si>
-  <si>
     <t>QUEENS MOTOR SPARES</t>
   </si>
   <si>
-    <t>045-838 1333 EMAIL: adribot@telkomsa.net</t>
+    <t>No. : 011 888 7944</t>
+  </si>
+  <si>
+    <t>043-726 0308</t>
+  </si>
+  <si>
+    <t>041-582 1788</t>
+  </si>
+  <si>
+    <t>045-838 1333</t>
+  </si>
+  <si>
+    <t>047-532 2246</t>
+  </si>
+  <si>
+    <t>(011) 334 0869</t>
   </si>
 </sst>
 </file>
@@ -752,6 +749,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1118,135 +1118,135 @@
         <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
         <v>91</v>
-      </c>
-      <c r="B47" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
         <v>95</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
         <v>97</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
